--- a/www/download/COUNTRY.WWW.rpO1.xlsx
+++ b/www/download/COUNTRY.WWW.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.783</t>
+          <t>83.0017362664145</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>86.4134594660474</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>102.014179313123</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6.672</t>
+          <t>290.539030642119</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>230.146087474519</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.098</t>
+          <t>245.732551893607</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.958</t>
+          <t>291.041461900099</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.077</t>
+          <t>267.002405200733</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7.851</t>
+          <t>245.713826288875</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8.707</t>
+          <t>262.224648142049</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9.294</t>
+          <t>281.057814717828</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9.845</t>
+          <t>257.596762257753</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>10.986</t>
+          <t>256.04215086888</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8.495</t>
+          <t>272.172645278223</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8.363</t>
+          <t>294.740221540565</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2660.653</t>
+          <t>2.21688051812419</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2706.543</t>
+          <t>2.11967467211267</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2747.777</t>
+          <t>2.04315044571125</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2779.313</t>
+          <t>2.02284825303909</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2813.91</t>
+          <t>2.16201602811269</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2881.293</t>
+          <t>2.06892646383661</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2937.735</t>
+          <t>1.99022958520788</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2954.355</t>
+          <t>2.04037021260873</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3027.326</t>
+          <t>2.20113984676448</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3086.349</t>
+          <t>2.07158115360121</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3143.524</t>
+          <t>2.10033424560233</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3193.889</t>
+          <t>2.02742225865349</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3225.066</t>
+          <t>1.99016344180161</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3270.744</t>
+          <t>1.91349055275255</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3280.621</t>
+          <t>1.87783399760359</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1340.302</t>
+          <t>3.88843920077044</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1366.883</t>
+          <t>3.75221839467526</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1397.427</t>
+          <t>3.65192462933106</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1415.446</t>
+          <t>3.65033962875793</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1441.207</t>
+          <t>3.79035687385083</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1481.326</t>
+          <t>3.75412394955774</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1514.24</t>
+          <t>3.63980951961713</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1528.087</t>
+          <t>3.70600724898331</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1560.787</t>
+          <t>3.88561946081681</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1599.028</t>
+          <t>3.72356091636825</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1636.236</t>
+          <t>3.76075839702692</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1673.185</t>
+          <t>3.68788946553967</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1700.913</t>
+          <t>3.56616495394837</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1735.034</t>
+          <t>3.46716508164478</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1740.403</t>
+          <t>3.38672112755226</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5050806.142</t>
+          <t>4.52705408088139</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5155267.84</t>
+          <t>4.40096911990381</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5214922.674</t>
+          <t>4.26905613849181</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5240263.707</t>
+          <t>4.3333959152702</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5294293.575</t>
+          <t>4.52819896191953</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5443795.236</t>
+          <t>4.46519699520139</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5634934.236</t>
+          <t>4.34461418739588</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5731499.926</t>
+          <t>4.46871744426194</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5933322.875</t>
+          <t>4.26425957043942</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6103273.608</t>
+          <t>4.4413222289187</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6167087.164</t>
+          <t>4.48238977090572</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6238229.391</t>
+          <t>4.37558379262167</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6308545.275</t>
+          <t>4.19260629204403</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6459964.684</t>
+          <t>4.02571883176331</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6489569.767</t>
+          <t>3.92085362205685</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2540163.195</t>
+          <t>1227455084501909</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2598384.756</t>
+          <t>1120023088409631</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2647332.327</t>
+          <t>1144909486964899</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2665359.155</t>
+          <t>1249605953610164</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2706491.456</t>
+          <t>1394272688795963</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2788332.154</t>
+          <t>1649386306493491</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2876310.617</t>
+          <t>1726668778175202</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2925557.023</t>
+          <t>1708021111465038</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3011822.532</t>
+          <t>1833014378406269</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3110191.477</t>
+          <t>1729576151812375</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3156833.451</t>
+          <t>1698456176737048</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3215874.427</t>
+          <t>1604798706017060</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3270922.466</t>
+          <t>1372327131471129</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3356370.108</t>
+          <t>1156124434078601</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3371243.035</t>
+          <t>1032410376514836</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>273107850025832</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>248373078612136</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>253145519603201</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>281264417587652</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>310568347939388</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>363440241884111</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>387781449881452</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>385282991911084</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>406839931799791</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>372536299313168</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>355132506524339</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>326829999837960</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>273513744130855</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>226403670441252</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>209997361257849</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>37535633898.0291</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>33896377400.4994</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>34986893839.6443</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>39506198462.4525</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>42605691408.3103</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>47763087740.3096</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>50764953605.4454</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>48709297242.2475</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>46037612927.8368</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>37678708642.2091</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>33712887606.7158</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>28693258172.0569</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>21313005493.7667</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>16054531040.7843</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>15984764407.9258</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>30484885.1135298</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>31234235.4846779</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>31299151.2366278</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>31329108.3113332</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28.17</t>
+          <t>32655313.5256945</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>33768522.6717612</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>33603008.965126</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>35093379.0794744</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>39548414.3301566</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>44563106.4386975</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>47934923.0020402</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>51813544.9978252</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>58502590.7790522</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>65687436.6897506</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>62306395.040176</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>56060688.4328249</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>122789481.799157</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>3.48247715311886</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>3.3494821684171</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>3.2372772660396</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>2.9497549327653</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>6782647.33020936</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>6921569.83571776</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>6799923.18790552</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>6672392.99758787</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>33.99</t>
+          <t>6921926.22014192</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>7097527.55120248</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>6957930.10248792</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>7076765.80994838</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>7851414.30481901</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>8707490.97895034</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>9293630.10720785</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>9845214.4705543</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>10985641.7858809</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>8495405.66030324</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>8363000.72243344</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>83.0017362664145</t>
+          <t>203765.885118044</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>86.4134594660474</t>
+          <t>181707.590908123</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>102.014179313123</t>
+          <t>181151.119608828</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>290.539030642119</t>
+          <t>198710.808193664</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>230.146087474519</t>
+          <t>215491.797384565</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>245.732551893607</t>
+          <t>245347.844588528</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>291.041461900099</t>
+          <t>256089.768486637</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>267.002405200733</t>
+          <t>252134.190908062</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>245.713826288875</t>
+          <t>260663.352836054</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>262.224648142049</t>
+          <t>232976.653387418</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>281.057814717828</t>
+          <t>217042.351029118</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>257.596762257753</t>
+          <t>195334.049913991</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>256.04215086888</t>
+          <t>160804.072462829</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>272.172645278223</t>
+          <t>130489.466036283</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>294.740221540565</t>
+          <t>120660.158827444</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15.221</t>
+          <t>5.69820404052734e-05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.429</t>
+          <t>4.67300415039062e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.319</t>
+          <t>-0.000850200653076172</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15.331</t>
+          <t>-0.000427961349487305</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>-0.000288963317871094</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16.435</t>
+          <t>0.00108575820922852</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16.416</t>
+          <t>0.000395298004150391</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16.947</t>
+          <t>0.000550746917724609</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18.855</t>
+          <t>0.00127077102661133</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20.892</t>
+          <t>0.0009307861328125</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22.393</t>
+          <t>-0.00123500823974609</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>24.078</t>
+          <t>-0.00172138214111328</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>26.916</t>
+          <t>0.000658035278320312</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>0.00131607055664062</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>-0.000125885009765625</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17.578</t>
+          <t>0.000293731689453125</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.826</t>
+          <t>-0.000148773193359375</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17.622</t>
+          <t>-0.00018763542175293</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.526</t>
+          <t>-0.000268459320068359</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18.139</t>
+          <t>-0.000238418579101562</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18.643</t>
+          <t>0.000670433044433594</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18.571</t>
+          <t>0.000319480895996094</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>-0.000435352325439453</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21.446</t>
+          <t>0.00110721588134766</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>23.768</t>
+          <t>0.000325679779052734</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25.436</t>
+          <t>0.000146389007568359</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>27.318</t>
+          <t>-7.62939453125e-05</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>30.664</t>
+          <t>2.38418579101562e-06</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>33.891</t>
+          <t>0.000103950500488281</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>32.314</t>
+          <t>0.000319004058837891</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>96.778</t>
+          <t>-2.288818359375e-05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>96.784</t>
+          <t>-7.05718994140625e-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>93.417</t>
+          <t>0.000128269195556641</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>91.398</t>
+          <t>-0.000523567199707031</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>93.05</t>
+          <t>-0.000224113464355469</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>93.252</t>
+          <t>0.000391006469726562</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>91.585</t>
+          <t>-1.62124633789062e-05</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>94.372</t>
+          <t>0.00112724304199219</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>105.628</t>
+          <t>0.000776290893554688</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>117.888</t>
+          <t>-0.000446319580078125</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>125.897</t>
+          <t>-0.00137519836425781</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>133.12</t>
+          <t>-0.00019073486328125</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>146.41</t>
+          <t>0.00150299072265625</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>104.856</t>
+          <t>0.000413894653320312</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>102.58</t>
+          <t>-8.67843627929688e-05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>913375.924626676</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>790333.926520911</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>767587.520836105</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>837460.386338666</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>936770.820425467</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>1045661.75072493</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>1062065.53344314</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>1060509.67601533</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>1127121.34598295</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>978203.901275626</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>917475.576696981</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>809183.148676848</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>651336.767564391</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>515401.412150719</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>466548.368776494</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>28.493</t>
+          <t>538300.496495408</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29.147</t>
+          <t>486166.072487321</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29.078</t>
+          <t>497712.147504319</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>28.869</t>
+          <t>551984.461040909</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29.949</t>
+          <t>613644.746936084</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30.886</t>
+          <t>712959.592469406</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30.695</t>
+          <t>748688.937108835</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31.979</t>
+          <t>741636.310427703</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>35.759</t>
+          <t>772927.281743552</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>706733.403454826</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>43.347</t>
+          <t>665612.603660183</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>46.869</t>
+          <t>606940.332396075</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>52.756</t>
+          <t>507852.358438195</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>58.372</t>
+          <t>415205.327517207</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>55.504</t>
+          <t>386524.45572199</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>221.69</t>
+          <t>5508610.12112343</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>211.97</t>
+          <t>5779500.38561317</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>204.32</t>
+          <t>5835243.83024285</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>202.28</t>
+          <t>5825939.74977636</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>216.2</t>
+          <t>6156193.03397744</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>206.89</t>
+          <t>6918403.94604327</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>199.02</t>
+          <t>6759373.98424006</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>204.04</t>
+          <t>7066389.67821914</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>220.11</t>
+          <t>8247724.71966098</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>207.16</t>
+          <t>10000629.7768033</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>210.03</t>
+          <t>11347033.5735735</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>202.74</t>
+          <t>12990862.3932813</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>199.02</t>
+          <t>15182374.0361702</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>191.35</t>
+          <t>17398629.7431671</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>187.78</t>
+          <t>13525729.2168622</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>388.84</t>
+          <t>173768886435423</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>375.22</t>
+          <t>161673410742864</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>365.19</t>
+          <t>165919004115801</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>365.03</t>
+          <t>185262168627426</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>379.04</t>
+          <t>210351108156213</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>375.41</t>
+          <t>266991626238887</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>363.98</t>
+          <t>278899495424259</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>370.6</t>
+          <t>280303697461607</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>388.56</t>
+          <t>309110083226742</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>372.36</t>
+          <t>308256493532678</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>376.08</t>
+          <t>311287272899649</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>368.79</t>
+          <t>304189281760405</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>356.62</t>
+          <t>260860542753836</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>346.72</t>
+          <t>222170402633947</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>338.67</t>
+          <t>166796942769945</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>452.71</t>
+          <t>5508610.12112343</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>440.1</t>
+          <t>5779500.38561317</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>426.91</t>
+          <t>5835243.83024285</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>433.34</t>
+          <t>5825939.74977636</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>452.82</t>
+          <t>6156193.03397744</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>446.52</t>
+          <t>6918403.94604327</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>434.46</t>
+          <t>6759373.98424006</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>446.87</t>
+          <t>7066389.67821914</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>426.43</t>
+          <t>8247724.71966098</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>444.13</t>
+          <t>10000629.7768033</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>448.24</t>
+          <t>11347033.5735735</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>437.56</t>
+          <t>12990862.3932813</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>419.26</t>
+          <t>15182374.0361702</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>402.57</t>
+          <t>17398629.7431671</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>392.09</t>
+          <t>13525729.2168622</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1432230992.224</t>
+          <t>173768886435423</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1315829474.09</t>
+          <t>161673410742864</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1367601983.424</t>
+          <t>165919004115801</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1534137394.158</t>
+          <t>185262168627426</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1726740922.087</t>
+          <t>210351108156213</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2054245779.906</t>
+          <t>266991626238887</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2199449966.436</t>
+          <t>278899495424259</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2191057216.827</t>
+          <t>280303697461607</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2339902827.841</t>
+          <t>309110083226742</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2181226012.109</t>
+          <t>308256493532678</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2092369187.848</t>
+          <t>311287272899649</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1938500216.637</t>
+          <t>304189281760405</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1637857305.439</t>
+          <t>260860542753836</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1358030488.716</t>
+          <t>222170402633947</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1268040252.559</t>
+          <t>166796942769945</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1224199698.078</t>
+          <t>-5.6843418860808e-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1080294276.538</t>
+          <t>3.62661012331955e-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1072647755.214</t>
+          <t>-3.21165316563565e-11</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1185379949.674</t>
+          <t>-3.78577169612981e-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1350080929.429</t>
+          <t>1.46940237755189e-11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1548966367.525</t>
+          <t>-7.40669747756328e-11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1608222440.363</t>
+          <t>-4.2774672692758e-11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1620551101.992</t>
+          <t>-8.15134626463987e-11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1759196168.317</t>
+          <t>-4.30873114964925e-11</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1564175877.953</t>
+          <t>-1.22213350550737e-11</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1501206560.297</t>
+          <t>-1.67176494869636e-10</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1353913096.398</t>
+          <t>1.92756033357e-10</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1107867202.976</t>
+          <t>-6.82121026329696e-13</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>894239014.122</t>
+          <t>-1.65414348884951e-11</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>811982408.231</t>
+          <t>-7.95239429862704e-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1227455084.502</t>
+          <t>0.00235748291015625</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1120023088.41</t>
+          <t>0.00096893310546875</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1144909486.965</t>
+          <t>-0.000886917114257812</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1249605953.61</t>
+          <t>-0.000553131103515625</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1394272688.796</t>
+          <t>0.000104904174804688</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1649386306.493</t>
+          <t>0.00231170654296875</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1726668778.175</t>
+          <t>-4.38690185546875e-05</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1708021111.465</t>
+          <t>-0.00284957885742188</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1833014378.406</t>
+          <t>0.00237274169921875</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1729576151.812</t>
+          <t>0.00283050537109375</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1698456176.737</t>
+          <t>-0.00226593017578125</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1604798706.017</t>
+          <t>-0.000269889831542969</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1372327131.471</t>
+          <t>-0.000911712646484375</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1156124434.079</t>
+          <t>0.00270271301269531</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1032410376.515</t>
+          <t>-0.000383377075195312</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>13044696.2493569</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>13290445.6572976</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>13109990.0098204</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>12744920.4409387</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>13099043.7183165</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>13472403.0542317</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>13139352.6461774</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>13610791.9504054</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>15302508.5889529</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>17477377.8788738</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>19036366.4925341</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>20789014.6159227</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>23566423.5210953</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>26482309.9296852</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>24546496.3928784</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>678094632.597</t>
+          <t>0.0304238278409743</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>618551952.822</t>
+          <t>0.0321717035765016</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>633138039.672</t>
+          <t>0.0356271734171024</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>698333205.702</t>
+          <t>0.0372549303996293</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>780881945.138</t>
+          <t>0.0387343770573523</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>915813135.321</t>
+          <t>0.0407372337988422</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>963764771.359</t>
+          <t>0.0418532770966377</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>962682215.922</t>
+          <t>0.0463244793865893</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1032524473.368</t>
+          <t>0.0470084313685068</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>967993984.836</t>
+          <t>0.049781213429953</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>930188819.507</t>
+          <t>0.0518732544549356</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>866789083.829</t>
+          <t>0.0547611702957098</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>733880459.136</t>
+          <t>0.0564493898568859</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>618480096.636</t>
+          <t>0.119295067164386</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>563479645.863</t>
+          <t>0.113208822600823</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>30.485</t>
+          <t>15221384.2665545</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31.234</t>
+          <t>15429141.5996516</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.299</t>
+          <t>15318515.8241342</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>31.329</t>
+          <t>15330655.2517422</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>32.655</t>
+          <t>15900170.5237955</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>33.769</t>
+          <t>16434756.3332771</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>33.603</t>
+          <t>16415915.2920473</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>35.093</t>
+          <t>16947272.3259557</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>39.548</t>
+          <t>18854816.2148648</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>44.563</t>
+          <t>20892271.5702224</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>47.935</t>
+          <t>22393234.0699656</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>51.814</t>
+          <t>24078135.639353</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>58.503</t>
+          <t>26916296.3842254</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>65.687</t>
+          <t>29800411.7686462</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>62.306</t>
+          <t>28449891.2350189</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>273107850.026</t>
+          <t>17578474.7456917</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>248373078.612</t>
+          <t>17825902.783292</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>253145519.603</t>
+          <t>17622048.5379238</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>281264417.588</t>
+          <t>17525832.2310874</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>310568347.939</t>
+          <t>18138832.5877258</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>363440241.884</t>
+          <t>18642809.0924923</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>387781449.881</t>
+          <t>18570731.973493</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>385282991.911</t>
+          <t>19189505.8865293</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>406839931.8</t>
+          <t>21446239.521659</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>372536299.313</t>
+          <t>23767828.4082607</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>355132506.524</t>
+          <t>25436229.899039</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>326829999.838</t>
+          <t>27318447.7177424</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>273513744.131</t>
+          <t>30664014.807903</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>226403670.441</t>
+          <t>33890653.6721761</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>209997361.258</t>
+          <t>32313568.4454114</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>96778054.8946727</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>96784030.5238092</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>93417153.378709</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>91398232.472819</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>93050073.1204685</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>93252101.2622381</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>91585051.8448396</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>94371503.0139495</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>105628209.099678</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>117888168.432761</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>125897169.697855</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>133119793.668559</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>146410390.501571</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>104856160.996644</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>102579524.861984</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>37535.634</t>
+          <t>15665921.4860808</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>33896.377</t>
+          <t>16039978.5631301</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34986.894</t>
+          <t>16510042.2759255</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>39506.198</t>
+          <t>16876192.8435332</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>42605.691</t>
+          <t>17406445.7421802</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>47763.088</t>
+          <t>18206570.9093391</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50764.954</t>
+          <t>18582323.4643653</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>48709.297</t>
+          <t>18756366.7829286</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>46037.613</t>
+          <t>19172979.4482314</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>37678.709</t>
+          <t>19672619.8776844</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>33712.888</t>
+          <t>20299938.7554035</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>28693.258</t>
+          <t>21058202.0944712</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>21313.005</t>
+          <t>21888974.336494</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>16054.531</t>
+          <t>22297839.3819118</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>15984.764</t>
+          <t>21620809.2690694</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>13565284.4902116</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>13894479.1788083</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>14326217.1663642</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>14685191.1371901</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>15181063.4012884</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>15966041.3616605</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16339719.4160127</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16492308.1631464</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>16849096.0929236</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>17328302.2869505</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>17894563.2368623</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>18608550.2435116</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>19310889.6876018</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>19686967.7166958</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>19023516.1251283</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9727006.21110924</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10035276.9766688</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10128112.3114608</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10077427.7870119</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10526162.8376043</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10896360.2025556</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10791064.6552599</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11448476.5559995</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>12816830.7228595</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14576107.0525679</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>15824326.0261009</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>17135010.161368</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>19250418.998403</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>21004228.4289976</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>19975907.9550105</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1224199698078205</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1080294276538341</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1072647755214426</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1185379949673948</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1350080929429389</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1548966367525213</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1608222440363484</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1620551101991687</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1759196168316781</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1564175877953471</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1501206560297307</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1353913096397593</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1107867202976497</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>894239014121504</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>811982408230791</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1432230992223992</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1315829474089882</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1367601983423946</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1534137394158348</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1726740922086799</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2054245779906052</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2199449966436216</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2191057216827426</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2339902827841108</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2181226012109208</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2092369187847597</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1938500216637389</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1637857305438727</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1358030488716240</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1268040252558506</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>678094632597201</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>618551952822051</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>633138039671845</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>698333205701714</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>780881945138307</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>915813135320759</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>963764771358579</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>962682215922411</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1032524473367735</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>967993984835703</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>930188819507162</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>866789083829037</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>733880459136436</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>618480096635874</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>563479645863411</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2660653299.68762</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2706543192.85967</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2747776983.70739</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2779312648.15922</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2813909726.61036</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2881293416.35052</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2937735363.00629</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2954355370.71242</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3027325963.39827</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3086349111.90897</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3143523990.29364</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3193889272.41759</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3225065864.56672</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3270744373.24015</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3280621015.7904</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1340302130.8872</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1366883339.16507</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1397427297.99206</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1415445994.83251</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1441207283.56612</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1481326410.23864</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1514240307.893</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1528087049.69162</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1560786843.92461</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1599028460.13363</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1636235991.91798</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1673184987.3684</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1700913042.44847</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1735034078.36997</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1740403487.76738</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5050806142338.25</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5155267839757.84</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5214922674001.2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5240263706642.2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5294293575380.68</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5443795235834.71</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5634934235581.34</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5731499925857.87</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5933322874864.6</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6103273607955.89</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6167087163760.7</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6238229391165.57</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6308545274711.33</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6459964683502.91</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6489569767236.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2540163194653.01</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2598384755765.98</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2647332326955.5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2665359154981.25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2706491456051.62</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2788332153999.34</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2876310616768.06</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2925557022779.32</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3011822532126.05</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3110191476674.07</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3156833450686.65</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3215874427204.57</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3270922465937.15</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3356370108232.97</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3371243035286.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228898648427933</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.231919837016752</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.233019160662987</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.235284951021892</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.240991356161571</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.247797250380012</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.249827856813299</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.256671032957441</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.249986894033455</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.274989880290778</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.282125256882255</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.287263989153529</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289429468407217</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.297021226523762</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.306401074424642</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.453619150842876</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.458991502302581</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.463130386661843</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.465589634981445</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.471018569897122</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.471636483388593</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.473224520750676</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.47349384372661</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.460707877633889</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472300993256089</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.470266756125835</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.469502423185547</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466965109699573</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.464136590079048</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.463349681517467</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.311210423639795</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.302816883592597</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.297578675591064</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.292853636915592</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.281718296863938</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.274294489159972</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.270675845366228</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.263563346248278</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.283033451269207</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.246437349393838</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.241336209934075</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.236961810604399</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.237333644837161</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.232570406340265</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.223977466996279</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.155282646906169</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.157701180745512</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.159117651873489</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.160829657779038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.164682133111337</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.168121531150933</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.170713780599449</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176732786541879</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.182257267892264</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.191332324721546</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.196486156235948</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.200505416481349</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.204207737261477</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.210861564497349</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.219257860870625</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.469773565988899</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.475494398270178</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.479710527481293</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.482224189295601</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.489192905849045</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.491557547666794</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.49292446743076</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.494602048512791</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.496828174229481</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.4980998533911</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.498983843039248</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.499095031787207</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.496367579988465</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.49598976431317</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.496499581531323</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.368672009238672</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.360532643119716</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.354900042802103</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.350674375095598</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.339853183220075</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.334049143400795</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.330089974152722</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.322393387130435</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.314642780119956</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.304296044170436</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.298258222998717</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.294127774003093</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.29315290501293</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.286876893426968</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.277970779745175</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>55182308.5366997</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>56556389.0503581</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>56598550.2992956</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>56060688.4328248</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>58306395.8341117</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>60817361.9019018</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>60202725.9733039</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>62263778.5854962</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>70209291.8668545</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>79623724.2735859</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>87525633.878685</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>95929115.303749</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>109397506.893586</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>122789481.799157</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>114158105.32809</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>28492989.6170379</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>29146972.6201288</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>29078015.2833797</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>28868950.3097123</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>29949423.6708065</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>30886319.2747992</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>30695232.7155385</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>31978700.6609161</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>35758542.8815301</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>40119766.8033391</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>43347211.2731476</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>46869212.7940502</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>52756188.9207813</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>58371735.6131579</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>55504275.79824</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4793954964.39064</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4967233143.90693</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5143827952.05915</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5218861965.06316</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>5277015495.56734</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5365828710.33491</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5457821230.57687</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5565008351.87191</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5670797423.00182</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5798409794.11186</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5943544186.73891</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>6092466572.53306</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>6255830382.90053</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>6332877240.97938</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>6470859610.00551</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
